--- a/feedback_cluster_view_for_google_sheets.xlsx
+++ b/feedback_cluster_view_for_google_sheets.xlsx
@@ -471,24 +471,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>119</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>sets_size_to_0</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>sets_size_to_0</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,10 +529,14 @@
       <c r="C4" t="n">
         <v>77</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>increment_size</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal, grow_check_goe, grow_check_plus_one, growth_check_with_size_function, increment_size, size_no_update</t>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal, grow_check_goe, grow_check_plus_one, growth_check_with_size_function</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -541,10 +545,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -561,10 +565,14 @@
       <c r="C5" t="n">
         <v>17</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>increment_size</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal, grow_check_goe, grow_check_other, increment_size, size_no_update</t>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal, grow_check_goe, grow_check_other, grow_check_plus_one</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -573,7 +581,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -600,7 +608,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal, grow_check_other, grow_check_plus_one</t>
+          <t>array_insert_uses_size, grow_check_equal, grow_check_other, grow_check_plus_one</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,7 +631,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count.</t>
+          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -636,12 +644,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal</t>
+          <t>grow_called_without_capacity_check, grow_check_equal, growth_check_with_size_function</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>grow_called_without_capacity_check, increment_size</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -659,32 +667,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count.</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>increment_size</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, grow_check_equal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>increment_size</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>grow_called_without_capacity_check, grow_check_equal</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>grow_called_without_capacity_check, increment_size</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -695,7 +703,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
+          <t>Incorrect: this `add` implementation does not increment the `size` field when it stores a new element, so the field can become smaller than the actual number of stored values. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -703,24 +711,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, increment_size</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>grow_called_without_capacity_check, grow_check_equal</t>
-        </is>
-      </c>
+          <t>grow_called_without_capacity_check, size_no_update</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>grow_called_without_capacity_check, size_no_update</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -731,7 +735,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Incorrect: this `add` implementation does not increment the `size` field when it stores a new element, so the field can become smaller than the actual number of stored values. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -739,13 +743,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -763,7 +767,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -771,13 +775,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -955,7 +959,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -963,13 +967,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
+          <t>calls_add, calls_add_only, size_no_update</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
+          <t>calls_add, calls_add_only, size_no_update</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -987,25 +991,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>calls_add, calls_add_only, size_no_update</t>
+          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>calls_add, calls_add_only, size_no_update</t>
+          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1019,7 +1023,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1217,22 +1221,22 @@
       <c r="C25" t="n">
         <v>57</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>assign_size_to_zero, size_not_reset</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>assign_size_to_zero</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>assign_size_to_zero</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1249,22 +1253,22 @@
       <c r="C26" t="n">
         <v>55</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>assign_size_to_zero, size_not_reset</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>assign_size_to_zero</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>assign_size_to_zero</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1307,7 +1311,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
+          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It also clears array contents or replaces the backing array, which is fine as an implementation detail. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1339,11 +1343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It also clears array contents or replaces the backing array, which is fine as an implementation detail. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
+          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1357,7 +1361,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -1453,7 +1457,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
@@ -1485,7 +1489,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
@@ -1599,7 +1603,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1613,7 +1617,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -1795,7 +1799,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1809,11 +1813,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>calls_contains, loop_standard_for</t>
+          <t>does_not_call_contains, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>3</v>
@@ -1831,12 +1835,12 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>data_length_check, loop_bound_other, no_loop, size_check</t>
+          <t>data_length_check, loop_bound_size, no_loop, size_check</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1845,7 +1849,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H44" t="n">
         <v>4</v>
@@ -1867,24 +1871,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>no_loop</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>size_check</t>
-        </is>
-      </c>
+          <t>no_loop, size_check</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>no_loop, size_check</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1936,7 +1936,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1948,7 +1948,7 @@
         <v>28</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1968,7 +1968,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2012,7 +2012,7 @@
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2032,7 +2032,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2064,7 +2064,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2160,7 +2160,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2256,7 +2256,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2279,28 +2279,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
         <is>
           <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2311,24 +2311,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>return_new_arraycollectioniterator</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>return_new_arraycollectioniterator</t>
+        </is>
+      </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2348,7 +2352,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2380,7 +2384,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator, returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2403,23 +2407,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>2</v>
       </c>
@@ -2601,17 +2597,9 @@
       <c r="C68" t="n">
         <v>1</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>1</v>
       </c>
@@ -2773,10 +2761,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H73" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -2805,7 +2793,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H74" t="n">
         <v>16</v>
@@ -2823,7 +2811,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
@@ -2837,7 +2825,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
         <v>3</v>
@@ -2967,12 +2955,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>two_loop_solution</t>
+          <t>loop_bound_data_length, two_loop_solution</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_data_length, loop_bound_other</t>
+          <t>item_removed, loop_bound_other</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3037,15 +3025,19 @@
       <c r="C81" t="n">
         <v>2</v>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>loop_bound_size</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, loop_bound_size, one_loop_solution, two_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, one_loop_solution, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>loop_bound_other, one_loop_solution, uses_contains</t>
+          <t>loop_bound_size, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3131,7 +3123,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3403,11 +3395,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3421,14 +3413,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -3439,7 +3431,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -3447,24 +3439,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove</t>
+          <t>does_not_call_remove</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>loop_other, loop_over_input_collection, loop_over_self_collection, size_change_nonstandard, size_no_update</t>
+          <t>calls_contains, does_not_call_contains, loop_other, loop_over_input_collection, loop_over_self_collection, size_change_nonstandard, size_no_update</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="G93" t="n">
         <v>3</v>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -3755,24 +3747,24 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>117</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>returns_size, returns_this_size</t>
-        </is>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>returns_size</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>returns_size</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -3835,7 +3827,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3853,7 +3845,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H105" t="n">
         <v>4</v>
@@ -3939,7 +3931,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3957,7 +3949,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H108" t="n">
         <v>7</v>
@@ -4025,11 +4017,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
+          <t>ignores_size_in_sort_scope, loop_bound_data_length, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H110" t="n">
         <v>3</v>
@@ -4046,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,14 +4090,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | BorneoElephant.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | CrabEatingMacaque.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Crustacea.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | NurseShark.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | OurPolicies.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | Seahorse.java | SiameseFightingFish.java | SiberianTiger.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tiger.java | TreeFrog.java | Uakari.java | Urochordata.java | Wasp.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
+          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | BorneoElephant.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | CrabEatingMacaque.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Crustacea.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | Newt.java | NurseShark.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | OurPolicies.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | Seahorse.java | SiameseFightingFish.java | SiberianTiger.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | Urochordata.java | Wasp.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -4117,43 +4109,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The constructor explicitly sets `size = 0`, so the logical element count starts at zero. It keeps `size` separate from capacity: array allocation determines `data.length`, while `size` represents how many logical elements are present.</t>
+          <t>The constructor explicitly sets `size = 0`, so the logical element count starts at zero. It keeps `size` separate from capacity: array allocation determines `data.length`, while `size` represents how many logical elements are present. Using `.length` here appears to be only for allocating the initial backing array, not for setting the count.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SeaUrchin.java | Tetra.java</t>
+          <t>Salamander.java</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ArrayCollection</t>
+          <t>add</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The constructor explicitly sets `size = 0`, so the logical element count starts at zero. It keeps `size` separate from capacity: array allocation determines `data.length`, while `size` represents how many logical elements are present. Using `.length` here appears to be only for allocating the initial backing array, not for setting the count.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Incorrect: this `add` implementation does not increment the `size` field when it stores a new element, so the field can become smaller than the actual number of stored values. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>grow_called_without_capacity_check, size_no_update</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Salamander.java</t>
+          <t>Crustacea.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -4165,23 +4161,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Incorrect: this `add` implementation does not increment the `size` field when it stores a new element, so the field can become smaller than the actual number of stored values. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>grow_missing, increment_size</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Crustacea.java | SiberianTiger.java</t>
+          <t>Possum.java</t>
         </is>
       </c>
     </row>
@@ -4193,23 +4189,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion.</t>
+          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>grow_missing, increment_size</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Possum.java</t>
+          <t>Bullfrog.java | Dormouse.java</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4217,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
+          <t>`add` increments `size`, so the count is updated when an insertion succeeds. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated. Because it looks for `null` positions, the method is partially reconstructing occupancy from array layout instead of treating `size` as the sole source of truth.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>grow_called_without_capacity_check, increment_size</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4237,7 +4233,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullfrog.java | Dormouse.java</t>
+          <t>HighlandCattle.java | Starfish.java</t>
         </is>
       </c>
     </row>
@@ -4254,18 +4250,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, increment_size</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HighlandCattle.java | Starfish.java</t>
+          <t>Moorhen.java</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4278,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>grow_check_equal, increment_size</t>
+          <t>growth_check_with_size_function, increment_size</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4293,7 +4289,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Moorhen.java</t>
+          <t>Newt.java</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4306,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4321,7 +4317,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LeopardCat.java | Ostrich.java</t>
+          <t>Ostrich.java | Prawn.java</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4362,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4377,7 +4373,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prawn.java</t>
+          <t>LeopardCat.java</t>
         </is>
       </c>
     </row>
@@ -4398,14 +4394,14 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | Caterpillar.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | FlyingSquirrel.java | FrilledLizard.java | Goose.java | Grasshopper.java | GreenBeeEater.java | Hamster.java | IndianPalmSquirrel.java | IndianRhinoceros.java | Kakapo.java | Kingfisher.java | Kiwi.java | Lizard.java | Llama.java | Mammalia.java | MaskedPalmCivet.java | Mole.java | OurPolicies.java | PatasMonkey.java | Quokka.java | RedKneeTarantula.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | StellersSeaCow.java | TreeFrog.java | WaterBuffalo.java | Yak.java | Zorse.java</t>
+          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | Caterpillar.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | CrestedPenguin.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | FlyingSquirrel.java | FrilledLizard.java | Goose.java | Grasshopper.java | GreenBeeEater.java | Hamster.java | IndianPalmSquirrel.java | IndianRhinoceros.java | Kakapo.java | Kingfisher.java | Kiwi.java | Lizard.java | Llama.java | Mammalia.java | MaskedPalmCivet.java | Mole.java | OurPolicies.java | PatasMonkey.java | Quokka.java | RedKneeTarantula.java | SeaOtter.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | StellersSeaCow.java | SunBear.java | Tiger.java | TreeFrog.java | WaterBuffalo.java | Yak.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -4422,18 +4418,18 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>array_insert_uses_size, grow_check_goe, increment_size</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CrestedPenguin.java | GreyReefShark.java | IndochineseTiger.java | Platypus.java | Rabbit.java | Scyphozoa.java | SeaOtter.java | Seahorse.java | SunBear.java | Tiger.java</t>
+          <t>AsiaticBlackBear.java | BlackRhinoceros.java | Dugong.java | Monkey.java | Okapi.java | Rhinoceros.java | SumatranTiger.java</t>
         </is>
       </c>
     </row>
@@ -4450,18 +4446,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_goe, increment_size</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AsiaticBlackBear.java | BlackRhinoceros.java | Dugong.java | Monkey.java | Okapi.java | Rhinoceros.java | SumatranTiger.java</t>
+          <t>BumbleBee.java | Hare.java | Impala.java | Parrot.java | SeaDragon.java | SeaUrchin.java</t>
         </is>
       </c>
     </row>
@@ -4478,18 +4474,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BumbleBee.java | CrabEatingMacaque.java | Orangutan.java | SeaDragon.java</t>
+          <t>GreyReefShark.java | Platypus.java | Rabbit.java | Scyphozoa.java | Seahorse.java</t>
         </is>
       </c>
     </row>
@@ -4534,18 +4530,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, increment_size</t>
+          <t>growth_check_with_size_function, increment_size</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Impala.java | Parrot.java | SeaUrchin.java</t>
+          <t>CrabEatingMacaque.java | LeopardTortoise.java</t>
         </is>
       </c>
     </row>
@@ -4562,18 +4558,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>grow_check_equal, increment_size</t>
+          <t>array_insert_uses_size, growth_check_with_size_function, increment_size</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hare.java</t>
+          <t>IndochineseTiger.java | Porcupine.java</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4586,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>growth_check_with_size_function, size_no_update</t>
+          <t>grow_check_plus_one, increment_size</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4601,7 +4597,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LeopardTortoise.java</t>
+          <t>Orangutan.java</t>
         </is>
       </c>
     </row>
@@ -4613,23 +4609,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, growth_check_with_size_function, increment_size</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Porcupine.java</t>
+          <t>BorneoElephant.java</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4637,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4650,14 +4646,14 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BorneoElephant.java</t>
+          <t>Panther.java | Robin.java</t>
         </is>
       </c>
     </row>
@@ -4669,23 +4665,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panther.java</t>
+          <t>Bobcat.java | Catfish.java | HoneyBee.java | MarineToad.java | SeaTurtle.java | SumatranElephant.java | Urochordata.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4693,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Duplicate detection is delegated to `contains`, so any boundary bug in `contains` also affects whether `add` accepts or rejects an insertion. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
+          <t>array_insert_uses_size, grow_check_other, increment_size</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4713,7 +4709,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Robin.java</t>
+          <t>Opossum.java</t>
         </is>
       </c>
     </row>
@@ -4730,18 +4726,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
+          <t>array_insert_uses_size, grow_check_plus_one, increment_size</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java | HoneyBee.java | MarineToad.java | SeaTurtle.java | SumatranElephant.java | Urochordata.java | YellowEyedPenguin.java</t>
+          <t>SabreToothedTiger.java</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4754,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_other, increment_size</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4769,7 +4765,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Opossum.java</t>
+          <t>Wasp.java</t>
         </is>
       </c>
     </row>
@@ -4781,23 +4777,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_plus_one, increment_size</t>
+          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SabreToothedTiger.java</t>
+          <t>Bivalvia.java | Crane.java | HornedFrog.java | KeelBilledToucan.java | Lionfish.java | Manatee.java | Salamander.java | Tapir.java | Tetra.java</t>
         </is>
       </c>
     </row>
@@ -4809,23 +4805,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. The method also iterates across capacity or searches for `null` slots instead of trusting `size` as the occupancy boundary. That is a boundary-design weakness even when `size` itself is updated.</t>
+          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, increment_size</t>
+          <t>array_insert_uses_size, grow_check_other, increment_size</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wasp.java</t>
+          <t>Bandicoot.java | Crab.java</t>
         </is>
       </c>
     </row>
@@ -4842,18 +4838,18 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_equal, increment_size</t>
+          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bivalvia.java | Crane.java | HornedFrog.java | KeelBilledToucan.java | Lionfish.java | Manatee.java | Salamander.java | Tapir.java</t>
+          <t>CrossRiverGorilla.java | SriLankanElephant.java</t>
         </is>
       </c>
     </row>
@@ -4870,18 +4866,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_called_without_capacity_check, increment_size</t>
+          <t>array_insert_uses_size, grow_check_goe, increment_size</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CrossRiverGorilla.java | NurseShark.java | SriLankanElephant.java</t>
+          <t>Gorilla.java | Woodpecker.java</t>
         </is>
       </c>
     </row>
@@ -4898,18 +4894,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_other, increment_size</t>
+          <t>array_insert_uses_size, grow_check_plus_one, increment_size</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bandicoot.java | Crab.java</t>
+          <t>NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -4926,74 +4922,74 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>array_insert_uses_size, grow_check_goe, increment_size</t>
+          <t>grow_check_equal, increment_size</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gorilla.java | Woodpecker.java</t>
+          <t>Uakari.java</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>addAll</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, size_no_update</t>
+          <t>calls_add, calls_add_only, size_no_update</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tetra.java</t>
+          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bivalvia.java | BlackRhinoceros.java | BorneoElephant.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | CrabEatingMacaque.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | OurPolicies.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | Sparrow.java | SpectacledBear.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tiger.java | TreeFrog.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>addAll</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>`add` writes the new element at index `size` and then increments `size`, which is the standard and correct way to maintain `size` as the logical count. Its capacity check uses the array length, which is appropriate only for deciding when to grow; `data.length` is capacity, not the logical count. Where it iterates, it uses `size` as the occupied prefix boundary, which matches the intended invariant.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>grow_called_without_capacity_check, increment_size</t>
+          <t>calls_add, calls_add_only, size_no_update</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uakari.java</t>
+          <t>Bandicoot.java | NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5001,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5014,14 +5010,14 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bivalvia.java | BlackRhinoceros.java | BorneoElephant.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | CrabEatingMacaque.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | OurPolicies.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | Sparrow.java | SpectacledBear.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tiger.java | TreeFrog.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
+          <t>Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5029,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5049,7 +5045,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bandicoot.java | NurseShark.java</t>
+          <t>Newt.java | SriLankanElephant.java</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5057,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Its own loop logic uses `size` as an occupancy boundary where needed. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. That means it inherits the `add` bug: every successful insertion handled by `addAll` can leave the `size` field wrong in the same way as `add`.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5077,7 +5073,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urochordata.java</t>
+          <t>SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5085,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. Because `add` updates `size` correctly, this delegation is the right design and keeps the count consistent. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. That means it inherits the `add` bug: every successful insertion handled by `addAll` can leave the `size` field wrong in the same way as `add`. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5105,7 +5101,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SriLankanElephant.java</t>
+          <t>Crustacea.java</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5113,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. That means it inherits the `add` bug: every successful insertion handled by `addAll` can leave the `size` field wrong in the same way as `add`.</t>
+          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5133,7 +5129,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SiberianTiger.java</t>
+          <t>MountainGorilla.java</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5141,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>`addAll` does not maintain `size` directly; it delegates each insertion to `add`. That means it inherits the `add` bug: every successful insertion handled by `addAll` can leave the `size` field wrong in the same way as `add`. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect. Its own loop logic uses `size` as an occupancy boundary where needed.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5161,7 +5157,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crustacea.java</t>
+          <t>Wasp.java</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5169,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect.</t>
+          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5182,14 +5178,14 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MountainGorilla.java</t>
+          <t>Bobcat.java | Catfish.java | Tetra.java</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5197,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect. Its own loop logic uses `size` as an occupancy boundary where needed.</t>
+          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>calls_add, calls_add_only, size_no_update</t>
+          <t>calls_add, calls_add_and_updates_size, increment_size, per_element_size_update, updates_size_directly</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5217,7 +5213,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wasp.java</t>
+          <t>SourcingOurContent.java</t>
         </is>
       </c>
     </row>
@@ -5229,79 +5225,79 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>`addAll` does not obviously manipulate `size`, so its effect on the count is indirect. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>calls_add, calls_add_only, size_no_update</t>
+          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java | Tetra.java</t>
+          <t>MarineToad.java | Seahorse.java</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>addAll</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended.</t>
+          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It also clears array contents or replaces the backing array, which is fine as an implementation detail. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>calls_add, calls_add_and_updates_size, increment_size, per_element_size_update, updates_size_directly</t>
+          <t>size_not_reset</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SourcingOurContent.java</t>
+          <t>Crustacea.java | Newt.java</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>addAll</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>`addAll` updates `size` directly while inserting elements; that can be correct if it increments once per element actually appended. Where it reasons about the backing array, it mixes in `.length`, which is capacity rather than logical size.</t>
+          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>does_not_call_add, increment_size, per_element_size_update, updates_size_directly</t>
+          <t>size_not_reset</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MarineToad.java | Seahorse.java</t>
+          <t>BorneoElephant.java | SiameseFightingFish.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5309,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It also clears array contents or replaces the backing array, which is fine as an implementation detail. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
+          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5322,14 +5318,14 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crustacea.java</t>
+          <t>FrilledLizard.java | IndianPalmSquirrel.java</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5337,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Incorrect: `clear()` does not reset `size`, so the backing array may be emptied or replaced while the logical count remains stale. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
+          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5350,14 +5346,14 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BorneoElephant.java | SiameseFightingFish.java | SiberianTiger.java</t>
+          <t>Kakapo.java</t>
         </is>
       </c>
     </row>
@@ -5369,23 +5365,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
+          <t>`clear()` reduces `size` incrementally inside the loop. That can reach the right final count if it executes once per stored element. It also clears array contents or replaces the backing array, which is fine as an implementation detail.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>size_not_reset</t>
+          <t>decrement_size</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FrilledLizard.java | IndianPalmSquirrel.java</t>
+          <t>Frigatebird.java</t>
         </is>
       </c>
     </row>
@@ -5397,23 +5393,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>`clear()` does not assign `size` directly, but it removes elements one by one so `size` is reduced indirectly through `remove`. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0. Because it loops over capacity while the collection is shrinking, it may skip elements or rely on shifting/null layout rather than using `size` cleanly as the source of truth.</t>
+          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It also clears array contents or replaces the backing array, which is fine as an implementation detail.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>size_not_reset</t>
+          <t>assign_size_to_zero</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kakapo.java</t>
+          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | AsianGiantHornet.java | AsiaticBlackBear.java | Bandicoot.java | Bobcat.java | Bullfrog.java | Catfish.java | Chicken.java | Cow.java | Crab.java | CrabEatingMacaque.java | CrossRiverGorilla.java | Discus.java | Dormouse.java | FlyingSquirrel.java | Goose.java | Grasshopper.java | Hamster.java | Hare.java | HighlandCattle.java | HornedFrog.java | IndianRhinoceros.java | IndochineseTiger.java | KeelBilledToucan.java | Kiwi.java | LeopardTortoise.java | Lionfish.java | Manatee.java | MaskedPalmCivet.java | Mole.java | Moorhen.java | NurseShark.java | Ostrich.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Rabbit.java | Robin.java | SabreToothedTiger.java | Salamander.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | SourcingOurContent.java | SumatranTiger.java | Tapir.java | Wasp.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -5425,135 +5421,131 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>`clear()` reduces `size` incrementally inside the loop. That can reach the right final count if it executes once per stored element. It also clears array contents or replaces the backing array, which is fine as an implementation detail.</t>
+          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>decrement_size</t>
+          <t>assign_size_to_zero</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Frigatebird.java</t>
+          <t>Anthozoa.java | ArcticWolf.java | Armadillo.java | Baboon.java | Bivalvia.java | BlackRhinoceros.java | BumbleBee.java | Caterpillar.java | Centipede.java | Cichlid.java | Crane.java | CrestedPenguin.java | Cuttlefish.java | Deer.java | Dhole.java | Dolphin.java | Dugong.java | Gorilla.java | GreenBeeEater.java | GreyReefShark.java | HoneyBee.java | Impala.java | Kingfisher.java | LeopardCat.java | Lizard.java | Llama.java | Mammalia.java | MarineToad.java | Monkey.java | MountainGorilla.java | Okapi.java | Opossum.java | Orangutan.java | OurPolicies.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | RedKneeTarantula.java | Rhinoceros.java | Scyphozoa.java | Seahorse.java | Skunk.java | SlowWorm.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SunBear.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | Urochordata.java | WaterBuffalo.java</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>contains</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It also clears array contents or replaces the backing array, which is fine as an implementation detail.</t>
+          <t>The method's search boundary is not obvious from static inspection. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>assign_size_to_zero</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | AsianGiantHornet.java | AsiaticBlackBear.java | Bandicoot.java | Bobcat.java | Catfish.java | Chicken.java | Cow.java | Crab.java | CrossRiverGorilla.java | Discus.java | FlyingSquirrel.java | Goose.java | Grasshopper.java | Hamster.java | Hare.java | HighlandCattle.java | HornedFrog.java | IndianRhinoceros.java | IndochineseTiger.java | KeelBilledToucan.java | Kiwi.java | Lionfish.java | Manatee.java | MaskedPalmCivet.java | Mole.java | Moorhen.java | NurseShark.java | Ostrich.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Rabbit.java | Robin.java | SabreToothedTiger.java | Salamander.java | SeaTurtle.java | SourcingOurContent.java | SumatranTiger.java | Tapir.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
+          <t>BlackRhinoceros.java | Bullfrog.java | Dormouse.java | FlyingSquirrel.java | Possum.java | SeaDragon.java | Yak.java</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>contains</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It also clears array contents or replaces the backing array, which is fine as an implementation detail.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>size_not_reset</t>
-        </is>
-      </c>
+          <t>The method's search boundary is not obvious from static inspection. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bullfrog.java | CrabEatingMacaque.java | Dormouse.java | LeopardTortoise.java | SeaDragon.java | SeaOtter.java | SeaUrchin.java | Wasp.java</t>
+          <t>Dolphin.java</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>contains</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
+          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>assign_size_to_zero</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anthozoa.java | ArcticWolf.java | Armadillo.java | Baboon.java | Bivalvia.java | BlackRhinoceros.java | Centipede.java | Cichlid.java | Crane.java | CrestedPenguin.java | Cuttlefish.java | Deer.java | Dhole.java | Dugong.java | Gorilla.java | GreenBeeEater.java | GreyReefShark.java | HoneyBee.java | Kingfisher.java | LeopardCat.java | Lizard.java | Llama.java | Mammalia.java | MarineToad.java | Monkey.java | MountainGorilla.java | Okapi.java | Opossum.java | OurPolicies.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | RedKneeTarantula.java | Rhinoceros.java | Scyphozoa.java | Seahorse.java | Skunk.java | SlowWorm.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | StellersSeaCow.java | SumatranElephant.java | Tiger.java | TreeFrog.java | Uakari.java | Urochordata.java | WaterBuffalo.java</t>
+          <t>Bobcat.java | Catfish.java | Centipede.java | Chicken.java | MarineToad.java | SiameseFightingFish.java | SiberianTiger.java | Sparrow.java | SunBear.java</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>contains</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>`clear()` resets `size` to 0, which is the essential requirement because the collection becomes logically empty. It does little or nothing to the backing array itself; that is acceptable only if `size` is still brought back to 0.</t>
+          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>size_not_reset</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BumbleBee.java | Caterpillar.java | Dolphin.java | Impala.java | Orangutan.java | Starfish.java | SunBear.java | Tetra.java</t>
+          <t>HoneyBee.java | Newt.java | Ostrich.java | Starfish.java | StellersSeaCow.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -5565,23 +5557,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The method's search boundary is not obvious from static inspection. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>loop_bound_data_length</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BlackRhinoceros.java | Bullfrog.java | Dormouse.java | FlyingSquirrel.java | Possum.java | SeaDragon.java | Yak.java</t>
+          <t>Okapi.java | Scyphozoa.java</t>
         </is>
       </c>
     </row>
@@ -5593,10 +5585,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The method's search boundary is not obvious from static inspection. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>loop_bound_other</t>
+        </is>
+      </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
@@ -5605,7 +5601,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolphin.java</t>
+          <t>Quokka.java</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5613,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>loop_bound_data_length</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5633,7 +5629,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java | Centipede.java | Chicken.java | MarineToad.java | SiameseFightingFish.java | SiberianTiger.java | Sparrow.java | SunBear.java</t>
+          <t>AfricanWildDog.java | Crustacea.java | Goose.java | Monkey.java | Panther.java | Prawn.java | SeaTurtle.java | SpectacledBear.java | Tapir.java</t>
         </is>
       </c>
     </row>
@@ -5645,23 +5641,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>loop_bound_size</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HoneyBee.java | Ostrich.java | Starfish.java | StellersSeaCow.java | Zorse.java</t>
+          <t>AfricanPenguin.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BorneoElephant.java | BumbleBee.java | Caterpillar.java | Cichlid.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | Discus.java | Dugong.java | Frigatebird.java | FrilledLizard.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | Hamster.java | Hare.java | HighlandCattle.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MaskedPalmCivet.java | Mole.java | MountainGorilla.java | NurseShark.java | Opossum.java | Parrot.java | Porcupine.java | Rabbit.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | SeaOtter.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | SriLankanElephant.java | SumatranElephant.java | SumatranTiger.java | Tiger.java | TreeFrog.java | Uakari.java | Wasp.java | WaterBuffalo.java | Woodpecker.java</t>
         </is>
       </c>
     </row>
@@ -5673,23 +5669,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
+          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>loop_bound_data_length</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Okapi.java | Scyphozoa.java</t>
+          <t>Armadillo.java | Cuttlefish.java | IndianRhinoceros.java | LeopardTortoise.java | Moorhen.java | Platypus.java | Seahorse.java | Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -5701,23 +5697,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
+          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>loop_bound_size</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Quokka.java</t>
+          <t>CrestedPenguin.java | GreyReefShark.java | IndochineseTiger.java | Orangutan.java | OurPolicies.java | PatasMonkey.java | RedKneeTarantula.java | SeaUrchin.java | Tetra.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -5729,135 +5725,135 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>`contains` scans the whole backing array or iterates to `.length` instead of stopping at `size`. That does not necessarily corrupt the `size` field itself, but it misuses capacity as though it were occupancy. This is a boundary bug risk: stale elements beyond `size` or `null` holes can affect the result even if `size` itself remains correct.</t>
+          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>loop_bound_data_length</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java | Crustacea.java | Goose.java | Monkey.java | Panther.java | Prawn.java | SeaTurtle.java | SpectacledBear.java | Tapir.java</t>
+          <t>CrabEatingMacaque.java</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>containsAll</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>loop_bound_size</t>
+          <t>calls_contains, loop_enhanced_for</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BorneoElephant.java | Cichlid.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | Discus.java | Dugong.java | Frigatebird.java | FrilledLizard.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | Hamster.java | Hare.java | HighlandCattle.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MaskedPalmCivet.java | Mole.java | MountainGorilla.java | NurseShark.java | Opossum.java | Parrot.java | Porcupine.java | Rabbit.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | SriLankanElephant.java | SumatranElephant.java | SumatranTiger.java | Tiger.java | TreeFrog.java | WaterBuffalo.java | Woodpecker.java</t>
+          <t>Bobcat.java | Catfish.java</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>containsAll</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>does_not_call_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Armadillo.java | BumbleBee.java | Caterpillar.java | Cuttlefish.java | IndianRhinoceros.java | LeopardTortoise.java | Moorhen.java | Platypus.java | SeaOtter.java | Seahorse.java | Uakari.java | Urochordata.java | Wasp.java</t>
+          <t>Ostrich.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>containsAll</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>loop_bound_size</t>
+          <t>calls_contains, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CrestedPenguin.java | GreyReefShark.java | OurPolicies.java | PatasMonkey.java | RedKneeTarantula.java | SeaUrchin.java | YellowEyedPenguin.java</t>
+          <t>Frigatebird.java</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>containsAll</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>`contains` searches only the prefix up to `size`, which is correct because only the first `size` positions are logically occupied. Its logic pays attention to `null` layout, so the method is partly inferring occupancy from array contents rather than relying purely on `size`. It keeps the logical element count (`size`) conceptually distinct from physical capacity.</t>
+          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>does_not_call_contains, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CrabEatingMacaque.java | IndochineseTiger.java | Orangutan.java | Tetra.java</t>
+          <t>HighlandCattle.java</t>
         </is>
       </c>
     </row>
@@ -5874,18 +5870,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for</t>
+          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java</t>
+          <t>Quokka.java</t>
         </is>
       </c>
     </row>
@@ -5902,18 +5898,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>does_not_call_contains, loop_enhanced_for, loop_other</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ostrich.java | Zorse.java</t>
+          <t>SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -5925,23 +5921,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>calls_contains, loop_over_input_collection, loop_standard_for</t>
+          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Frigatebird.java</t>
+          <t>AfricanPenguin.java | Amphibia.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | BorneoElephant.java | BumbleBee.java | Caterpillar.java | Cow.java | Crab.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dugong.java | Grasshopper.java | GreenBeeEater.java | Hare.java | Impala.java | IndianRhinoceros.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Manatee.java | MaskedPalmCivet.java | Moorhen.java | Opossum.java | Orangutan.java | OurPolicies.java | Parrot.java | Porcupine.java | RedKneeTarantula.java | Robin.java | SabreToothedTiger.java | Salamander.java | SeaOtter.java | SlowWorm.java | SourcingOurContent.java | SumatranElephant.java | SumatranTiger.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -5953,23 +5949,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_over_input_collection, loop_standard_for</t>
+          <t>calls_contains</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HighlandCattle.java</t>
+          <t>Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | CrabEatingMacaque.java | Gorilla.java | GreyReefShark.java | Hamster.java | IndochineseTiger.java | Llama.java | Platypus.java | Rabbit.java | Rhinoceros.java | Seahorse.java | Skunk.java | Wasp.java</t>
         </is>
       </c>
     </row>
@@ -5981,23 +5977,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>calls_contains, loop_enhanced_for, loop_other</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quokka.java</t>
+          <t>Bivalvia.java | Cichlid.java | Mammalia.java | SeaUrchin.java</t>
         </is>
       </c>
     </row>
@@ -6009,23 +6005,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>`containsAll` does not obviously reference `size`; it mainly depends on helper calls and collection semantics.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_enhanced_for, loop_other</t>
+          <t>does_not_call_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SiberianTiger.java</t>
+          <t>FrilledLizard.java | IndianPalmSquirrel.java | MountainGorilla.java</t>
         </is>
       </c>
     </row>
@@ -6042,18 +6038,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>calls_contains, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="E72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Amphibia.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | BorneoElephant.java | BumbleBee.java | Caterpillar.java | Cow.java | Crab.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dugong.java | Grasshopper.java | GreenBeeEater.java | Hare.java | Impala.java | IndianRhinoceros.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Manatee.java | MaskedPalmCivet.java | Moorhen.java | Opossum.java | Orangutan.java | OurPolicies.java | Parrot.java | Porcupine.java | RedKneeTarantula.java | Robin.java | SabreToothedTiger.java | Salamander.java | SeaOtter.java | SlowWorm.java | SourcingOurContent.java | SumatranElephant.java | SumatranTiger.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | YellowEyedPenguin.java</t>
+          <t>HornedFrog.java | Mole.java</t>
         </is>
       </c>
     </row>
@@ -6070,18 +6066,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>calls_contains</t>
+          <t>calls_contains, loop_enhanced_for, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | CrabEatingMacaque.java | Gorilla.java | GreyReefShark.java | Hamster.java | IndochineseTiger.java | Llama.java | Platypus.java | Rabbit.java | Rhinoceros.java | Seahorse.java | Skunk.java | Wasp.java</t>
+          <t>Bandicoot.java</t>
         </is>
       </c>
     </row>
@@ -6098,18 +6094,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_other</t>
+          <t>does_not_call_contains, loop_enhanced_for, loop_other</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bivalvia.java | Cichlid.java | Mammalia.java | SeaUrchin.java</t>
+          <t>PatasMonkey.java</t>
         </is>
       </c>
     </row>
@@ -6126,18 +6122,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>calls_contains, loop_other, loop_standard_for</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FrilledLizard.java | IndianPalmSquirrel.java | MountainGorilla.java</t>
+          <t>Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -6149,23 +6145,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>calls_contains, loop_over_input_collection, loop_standard_for</t>
+          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HornedFrog.java | Mole.java</t>
+          <t>AfricanWildDog.java | Centipede.java | Chicken.java | Goose.java | HoneyBee.java | Monkey.java | Okapi.java | Scyphozoa.java | SiameseFightingFish.java | Starfish.java | StellersSeaCow.java</t>
         </is>
       </c>
     </row>
@@ -6177,23 +6173,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_over_input_collection, loop_standard_for</t>
+          <t>calls_contains, loop_enhanced_for, loop_other</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bandicoot.java</t>
+          <t>MarineToad.java | Panther.java | Prawn.java | Sparrow.java | SunBear.java</t>
         </is>
       </c>
     </row>
@@ -6205,23 +6201,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_enhanced_for, loop_other</t>
+          <t>calls_contains</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PatasMonkey.java</t>
+          <t>Crustacea.java | SeaTurtle.java | SpectacledBear.java | Tapir.java</t>
         </is>
       </c>
     </row>
@@ -6233,23 +6229,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` already uses `size` as the occupied boundary, this is the correct design.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>calls_contains, loop_other, loop_standard_for</t>
+          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Urochordata.java</t>
+          <t>Bullfrog.java | Dolphin.java | Dormouse.java | Possum.java | SeaDragon.java | Yak.java</t>
         </is>
       </c>
     </row>
@@ -6261,23 +6257,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>does_not_call_contains</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java | Centipede.java | Chicken.java | Goose.java | HoneyBee.java | Monkey.java | Okapi.java | Scyphozoa.java | SiameseFightingFish.java | Starfish.java | StellersSeaCow.java</t>
+          <t>BlackRhinoceros.java</t>
         </is>
       </c>
     </row>
@@ -6289,23 +6285,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
+          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_other</t>
+          <t>calls_contains</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MarineToad.java | Panther.java | Prawn.java | Sparrow.java | SunBear.java</t>
+          <t>FlyingSquirrel.java</t>
         </is>
       </c>
     </row>
@@ -6317,23 +6313,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Because `contains` scans capacity/null layout instead of stopping at `size`, `containsAll` inherits the same boundary mistake.</t>
+          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>calls_contains</t>
+          <t>does_not_call_contains, loop_over_input_collection, loop_standard_for</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Crustacea.java | SeaTurtle.java | SpectacledBear.java | Tapir.java</t>
+          <t>Newt.java | NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -6345,23 +6341,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
+          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>calls_contains, loop_enhanced_for, loop_over_input_collection</t>
+          <t>calls_contains, loop_standard_for</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bullfrog.java | Dolphin.java | Dormouse.java | Possum.java | SeaDragon.java | Yak.java</t>
+          <t>Kakapo.java</t>
         </is>
       </c>
     </row>
@@ -6373,12 +6369,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
+          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>does_not_call_contains</t>
+          <t>does_not_call_contains, loop_other, loop_standard_for</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -6389,80 +6385,80 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BlackRhinoceros.java</t>
+          <t>SriLankanElephant.java</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>containsAll</t>
+          <t>isEmpty</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>`containsAll` is mostly a wrapper around `contains`, so it does not usually change `size` directly. Its correctness therefore depends on the quality of the underlying `contains` method.</t>
+          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>calls_contains</t>
+          <t>no_loop, size_check</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FlyingSquirrel.java</t>
+          <t>AfricanPenguin.java | Amphibia.java | AsianGiantHornet.java | Bivalvia.java | Bobcat.java | Bullfrog.java | Catfish.java | Centipede.java | Chicken.java | Cow.java | Crane.java | Cuttlefish.java | Dolphin.java | Dormouse.java | Gorilla.java | Hare.java | HornedFrog.java | IndochineseTiger.java | Kingfisher.java | Kiwi.java | LeopardCat.java | MaskedPalmCivet.java | Moorhen.java | NurseShark.java | Opossum.java | Ostrich.java | Panther.java | Porcupine.java | Prawn.java | Rabbit.java | Rhinoceros.java | Scyphozoa.java | SeaOtter.java | SeaTurtle.java | Seahorse.java | SiameseFightingFish.java | Sparrow.java | SriLankanElephant.java | StellersSeaCow.java | Tapir.java | Tetra.java | Urochordata.java | Wasp.java | Yak.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>containsAll</t>
+          <t>isEmpty</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
+          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>calls_contains, loop_standard_for</t>
+          <t>no_loop</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kakapo.java</t>
+          <t>BorneoElephant.java | Caterpillar.java | CrabEatingMacaque.java | FlyingSquirrel.java | FrilledLizard.java | Impala.java | IndianRhinoceros.java | Mammalia.java | Newt.java | PatasMonkey.java | Platypus.java | Possum.java</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>containsAll</t>
+          <t>isEmpty</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
+          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_over_input_collection, loop_standard_for</t>
+          <t>loop_bound_size, size_check</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -6473,24 +6469,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NurseShark.java</t>
+          <t>IndianPalmSquirrel.java</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>containsAll</t>
+          <t>isEmpty</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>`containsAll` performs its own checks and uses `size` as the occupied-prefix boundary, which is appropriate.</t>
+          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>does_not_call_contains, loop_other, loop_standard_for</t>
+          <t>data_length_check, no_loop</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -6501,7 +6497,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SriLankanElephant.java</t>
+          <t>Quokka.java</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6509,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
+          <t>`isEmpty()` checks whether `size` is zero, which is the correct and simplest interpretation of emptiness for this data structure.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6522,14 +6518,14 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Amphibia.java | AsianGiantHornet.java | Bobcat.java | Catfish.java | Centipede.java | Chicken.java | Cow.java | Crane.java | Cuttlefish.java | Gorilla.java | Hare.java | HornedFrog.java | IndochineseTiger.java | Kingfisher.java | Kiwi.java | LeopardCat.java | Moorhen.java | NurseShark.java | Opossum.java | Ostrich.java | Porcupine.java | Prawn.java | Rabbit.java | Rhinoceros.java | Scyphozoa.java | SeaTurtle.java | Seahorse.java | SiameseFightingFish.java | Sparrow.java | SriLankanElephant.java | StellersSeaCow.java | Tapir.java | Urochordata.java | Yak.java | YellowEyedPenguin.java</t>
+          <t>Anthozoa.java | ArcticWolf.java | Armadillo.java | AsiaticBlackBear.java | Baboon.java | BlackRhinoceros.java | BumbleBee.java | Cichlid.java | Crab.java | CrestedPenguin.java | CrossRiverGorilla.java | Deer.java | Discus.java | Dugong.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | HighlandCattle.java | HoneyBee.java | KeelBilledToucan.java | Lionfish.java | Lizard.java | Llama.java | Manatee.java | Mole.java | Monkey.java | MountainGorilla.java | Okapi.java | Orangutan.java | OurPolicies.java | Parrot.java | RedKneeTarantula.java | SabreToothedTiger.java | Salamander.java | SeaUrchin.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | SpectacledBear.java | Starfish.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | TreeFrog.java | WaterBuffalo.java | Woodpecker.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -6541,23 +6537,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
+          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>no_loop</t>
+          <t>loop_bound_other</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bivalvia.java | BorneoElephant.java | Bullfrog.java | Caterpillar.java | CrabEatingMacaque.java | Dolphin.java | Dormouse.java | FlyingSquirrel.java | FrilledLizard.java | Impala.java | IndianRhinoceros.java | Mammalia.java | MaskedPalmCivet.java | Panther.java | PatasMonkey.java | Platypus.java | Possum.java | SeaOtter.java | Tetra.java | Wasp.java</t>
+          <t>Dhole.java | LeopardTortoise.java | MarineToad.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -6569,23 +6565,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
+          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>loop_bound_other, size_check</t>
+          <t>loop_bound_data_length</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>IndianPalmSquirrel.java</t>
+          <t>Hamster.java | Robin.java | Tiger.java | Uakari.java</t>
         </is>
       </c>
     </row>
@@ -6597,23 +6593,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The emptiness test does not clearly reveal whether it trusts `size` or reconstructs occupancy indirectly.</t>
+          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>data_length_check, no_loop</t>
+          <t>loop_bound_size</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Quokka.java</t>
+          <t>Bandicoot.java | Frigatebird.java</t>
         </is>
       </c>
     </row>
@@ -6625,23 +6621,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>`isEmpty()` checks whether `size` is zero, which is the correct and simplest interpretation of emptiness for this data structure.</t>
+          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>no_loop, size_check</t>
+          <t>no_loop</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anthozoa.java | ArcticWolf.java | Armadillo.java | AsiaticBlackBear.java | Baboon.java | BlackRhinoceros.java | BumbleBee.java | Cichlid.java | Crab.java | CrossRiverGorilla.java | Deer.java | Discus.java | Dugong.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | HighlandCattle.java | HoneyBee.java | KeelBilledToucan.java | Lionfish.java | Lizard.java | Llama.java | Manatee.java | Mole.java | Monkey.java | MountainGorilla.java | Okapi.java | OurPolicies.java | RedKneeTarantula.java | SabreToothedTiger.java | Salamander.java | SeaUrchin.java | Skunk.java | SourcingOurContent.java | SpectacledBear.java | Starfish.java | SumatranElephant.java | SumatranTiger.java | TreeFrog.java | WaterBuffalo.java | Woodpecker.java | Zorse.java</t>
+          <t>Crustacea.java | SeaDragon.java</t>
         </is>
       </c>
     </row>
@@ -6653,23 +6649,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>`isEmpty()` checks whether `size` is zero, which is the correct and simplest interpretation of emptiness for this data structure.</t>
+          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>no_loop</t>
+          <t>loop_bound_data_length, size_check</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CrestedPenguin.java | Orangutan.java | Parrot.java | SlowWorm.java | SunBear.java</t>
+          <t>Goose.java | Kakapo.java</t>
         </is>
       </c>
     </row>
@@ -6686,158 +6682,154 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>loop_bound_other</t>
+          <t>data_length_check, loop_bound_data_length</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dhole.java | LeopardTortoise.java | MarineToad.java | SiberianTiger.java</t>
+          <t>AfricanWildDog.java</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>isEmpty</t>
+          <t>iterator</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. No iterator-specific `remove()` method was parsed, so I cannot verify deletion through the iterator.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>loop_bound_data_length</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hamster.java | Robin.java | Tiger.java | Uakari.java</t>
+          <t>AfricanPenguin.java</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>isEmpty</t>
+          <t>iterator</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>loop_bound_size</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bandicoot.java | Frigatebird.java</t>
+          <t>SabreToothedTiger.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>isEmpty</t>
+          <t>iterator</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>no_loop</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crustacea.java | SeaDragon.java</t>
+          <t>MarineToad.java</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>isEmpty</t>
+          <t>iterator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>loop_bound_data_length, size_check</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Goose.java | Kakapo.java</t>
+          <t>Crab.java</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>isEmpty</t>
+          <t>iterator</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>`isEmpty()` scans the backing array or relies on `null` layout instead of simply testing `size == 0`. That is a misuse of the representation boundary even if the answer often matches.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>data_length_check, loop_bound_data_length</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java</t>
+          <t>Robin.java</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6841,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. No iterator-specific `remove()` method was parsed, so I cannot verify deletion through the iterator.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6865,7 +6857,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java</t>
+          <t>Starfish.java</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6869,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6886,14 +6878,14 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SabreToothedTiger.java | SiberianTiger.java</t>
+          <t>BorneoElephant.java | Kakapo.java | Kiwi.java | SeaDragon.java</t>
         </is>
       </c>
     </row>
@@ -6905,23 +6897,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MarineToad.java</t>
+          <t>Crustacea.java | HornedFrog.java</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6921,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6949,7 +6937,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Crab.java</t>
+          <t>Goose.java</t>
         </is>
       </c>
     </row>
@@ -6961,23 +6949,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Robin.java</t>
+          <t>Orangutan.java</t>
         </is>
       </c>
     </row>
@@ -6989,14 +6973,10 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
         <v>1</v>
       </c>
@@ -7005,7 +6985,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Starfish.java</t>
+          <t>Yak.java</t>
         </is>
       </c>
     </row>
@@ -7017,7 +6997,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` compares against array length, so the iterator can walk into unused capacity slots. That is a boundary bug even if the `size` field elsewhere is correct. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7026,14 +7006,14 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BorneoElephant.java | Kakapo.java | Kiwi.java | SeaDragon.java</t>
+          <t>Baboon.java | Chicken.java | Crane.java | Cuttlefish.java | IndianPalmSquirrel.java | Kingfisher.java | Monkey.java | Opossum.java | Rabbit.java | Rhinoceros.java | SeaOtter.java | SumatranElephant.java | Tetra.java | WaterBuffalo.java</t>
         </is>
       </c>
     </row>
@@ -7045,19 +7025,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crustacea.java</t>
+          <t>ArcticWolf.java | Quokka.java | Uakari.java</t>
         </is>
       </c>
     </row>
@@ -7069,23 +7049,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HornedFrog.java</t>
+          <t>BlackRhinoceros.java | GreyReefShark.java | SeaUrchin.java | SlowWorm.java | Tapir.java</t>
         </is>
       </c>
     </row>
@@ -7097,23 +7077,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Goose.java</t>
+          <t>Gorilla.java</t>
         </is>
       </c>
     </row>
@@ -7125,23 +7101,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Orangutan.java</t>
+          <t>Bobcat.java | Catfish.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -7153,23 +7129,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yak.java</t>
+          <t>NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7153,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7190,14 +7162,14 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Baboon.java | Chicken.java | Crane.java | Cuttlefish.java | IndianPalmSquirrel.java | Kingfisher.java | Monkey.java | Opossum.java | Rabbit.java | Rhinoceros.java | SeaOtter.java | SumatranElephant.java | Tetra.java | WaterBuffalo.java</t>
+          <t>RedKneeTarantula.java</t>
         </is>
       </c>
     </row>
@@ -7209,23 +7181,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ArcticWolf.java | Quokka.java | Uakari.java</t>
+          <t>Discus.java | Lizard.java | MountainGorilla.java | Parrot.java</t>
         </is>
       </c>
     </row>
@@ -7237,23 +7209,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BlackRhinoceros.java | GreyReefShark.java | SeaUrchin.java | SlowWorm.java | Tapir.java</t>
+          <t>HighlandCattle.java | Panther.java | Scyphozoa.java</t>
         </is>
       </c>
     </row>
@@ -7265,23 +7233,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gorilla.java</t>
+          <t>BumbleBee.java</t>
         </is>
       </c>
     </row>
@@ -7293,23 +7261,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java | YellowEyedPenguin.java</t>
+          <t>SriLankanElephant.java</t>
         </is>
       </c>
     </row>
@@ -7321,23 +7285,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NurseShark.java</t>
+          <t>Dolphin.java | Dugong.java</t>
         </is>
       </c>
     </row>
@@ -7349,23 +7313,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RedKneeTarantula.java</t>
+          <t>Newt.java</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7337,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7393,7 +7353,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Discus.java | Lizard.java | MountainGorilla.java | Parrot.java</t>
+          <t>Bullfrog.java | Dormouse.java | Possum.java | Tiger.java</t>
         </is>
       </c>
     </row>
@@ -7405,23 +7365,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HighlandCattle.java | Panther.java | Scyphozoa.java</t>
+          <t>Amphibia.java | Armadillo.java | AsianGiantHornet.java | Bandicoot.java | Bivalvia.java | Caterpillar.java | Cichlid.java | CrestedPenguin.java | FlyingSquirrel.java | Hamster.java | Impala.java | KeelBilledToucan.java | LeopardTortoise.java | Lionfish.java | Manatee.java | Mole.java | Moorhen.java | Okapi.java | SiameseFightingFish.java | Skunk.java | SourcingOurContent.java | SpectacledBear.java | StellersSeaCow.java | SumatranTiger.java | TreeFrog.java | Urochordata.java | Wasp.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -7433,23 +7393,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>return_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BumbleBee.java</t>
+          <t>Frigatebird.java | FrilledLizard.java | Hare.java | IndianRhinoceros.java | MaskedPalmCivet.java | Ostrich.java</t>
         </is>
       </c>
     </row>
@@ -7461,23 +7417,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` could not be classified confidently from static inspection. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>return_new_arraycollectioniterator</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SriLankanElephant.java</t>
+          <t>AsiaticBlackBear.java | Dhole.java | Salamander.java | SunBear.java | Woodpecker.java</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7445,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7505,7 +7461,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dolphin.java | Dugong.java</t>
+          <t>PatasMonkey.java | SeaTurtle.java</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7473,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7526,14 +7482,14 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E125" t="b">
         <v>1</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bullfrog.java | Dormouse.java | Possum.java | Tiger.java</t>
+          <t>Mammalia.java</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7501,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7554,14 +7510,14 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Amphibia.java | Armadillo.java | AsianGiantHornet.java | Bandicoot.java | Bivalvia.java | Caterpillar.java | Cichlid.java | CrestedPenguin.java | FlyingSquirrel.java | Hamster.java | Impala.java | KeelBilledToucan.java | LeopardTortoise.java | Lionfish.java | Manatee.java | Mole.java | Moorhen.java | Okapi.java | SiameseFightingFish.java | Skunk.java | SourcingOurContent.java | SpectacledBear.java | StellersSeaCow.java | SumatranTiger.java | TreeFrog.java | Urochordata.java | Wasp.java | Zorse.java</t>
+          <t>Anthozoa.java | Cow.java | CrossRiverGorilla.java | Grasshopper.java | HoneyBee.java | IndochineseTiger.java</t>
         </is>
       </c>
     </row>
@@ -7573,23 +7529,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
-        </is>
-      </c>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Frigatebird.java | Hare.java | IndianRhinoceros.java | MaskedPalmCivet.java | Ostrich.java</t>
+          <t>Platypus.java | Porcupine.java | Prawn.java</t>
         </is>
       </c>
     </row>
@@ -7601,19 +7553,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>return_new_arraycollectioniterator</t>
+        </is>
+      </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FrilledLizard.java</t>
+          <t>CrabEatingMacaque.java | Llama.java | OurPolicies.java | Seahorse.java | Sparrow.java</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7581,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7634,14 +7590,14 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E129" t="b">
         <v>1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AsiaticBlackBear.java | Dhole.java | Salamander.java | SunBear.java | Woodpecker.java</t>
+          <t>Centipede.java</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7609,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7662,14 +7618,14 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" t="b">
         <v>1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PatasMonkey.java | SeaTurtle.java</t>
+          <t>Deer.java | GreenBeeEater.java | LeopardCat.java</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7637,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Incorrect: iterator `remove()` changes array contents or removal state without any visible `size` update. That means iteration-based deletion can leave the logical count stale.</t>
+          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7697,199 +7653,203 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mammalia.java</t>
+          <t>AfricanWildDog.java</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator</t>
+          <t>loop_bound_other, one_loop_solution</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E132" t="b">
         <v>1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anthozoa.java | Cow.java | CrossRiverGorilla.java | Grasshopper.java | HoneyBee.java | IndochineseTiger.java</t>
+          <t>BlackRhinoceros.java | GreenBeeEater.java</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>item_removed, iterator_removal, loop_bound_other, one_loop_solution, uses_contains</t>
+        </is>
+      </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Platypus.java | Prawn.java</t>
+          <t>SlowWorm.java</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` delegates to the collection's main `remove` logic instead of editing `size` separately. That is correct if the outer `remove` method maintains `size` exactly once.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>returns_iterator_variable_initialized_with_new_arraycollectioniterator</t>
+          <t>item_removed, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Porcupine.java</t>
+          <t>Monkey.java | Quokka.java</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator</t>
+          <t>loop_bound_size, one_loop_solution</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CrabEatingMacaque.java | Llama.java | OurPolicies.java | Seahorse.java | Sparrow.java</t>
+          <t>Dugong.java</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. It also guards the logical end of iteration with `NoSuchElementException`, which is standard behavior. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator</t>
+          <t>item_removed, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="b">
         <v>1</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Centipede.java</t>
+          <t>Bobcat.java | Catfish.java</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator</t>
+          <t>item_removed, loop_bound_other, one_loop_solution</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Deer.java | GreenBeeEater.java | LeopardCat.java</t>
+          <t>BorneoElephant.java</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iterator</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>`iterator()` itself simply creates the iterator object; the important size behavior is in `hasNext`, `next`, and iterator `remove`. `hasNext()` uses `index &lt; size`, which is correct because iteration should stop at the logical count rather than at capacity. `next()` advances the iterator index after returning the current logical element, which is the expected interaction with `size`. Iterator `remove()` shifts/removes elements and decrements `size` itself, which is acceptable if the shift is correct and the decrement happens exactly once. Its internal boundary logic also leans on capacity/null layout rather than the `size` prefix.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>return_new_arraycollectioniterator</t>
+          <t>loop_bound_data_length, one_loop_solution</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="b">
         <v>1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java</t>
+          <t>SeaTurtle.java | Starfish.java</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7861,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>loop_bound_other, one_loop_solution</t>
+          <t>item_removed, loop_bound_data_length, two_loop_solution</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -7917,7 +7877,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BlackRhinoceros.java | GreenBeeEater.java</t>
+          <t>Crustacea.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -7929,12 +7889,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large.</t>
+          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>item_removed, iterator_removal, loop_bound_other, one_loop_solution, uses_contains</t>
+          <t>loop_bound_data_length, loop_bound_other, two_loop_solution</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -7945,7 +7905,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SlowWorm.java</t>
+          <t>SeaDragon.java</t>
         </is>
       </c>
     </row>
@@ -7957,23 +7917,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_size, two_loop_solution</t>
+          <t>loop_bound_size, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" t="b">
         <v>1</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Monkey.java | Quokka.java</t>
+          <t>IndianPalmSquirrel.java</t>
         </is>
       </c>
     </row>
@@ -7985,12 +7945,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>loop_bound_size, one_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -8001,7 +7961,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dugong.java</t>
+          <t>Opossum.java</t>
         </is>
       </c>
     </row>
@@ -8013,23 +7973,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_size, two_loop_solution</t>
+          <t>loop_bound_other, one_loop_solution</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E143" t="b">
         <v>1</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java</t>
+          <t>Newt.java | Tiger.java | Yak.java</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8001,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_other, one_loop_solution</t>
+          <t>decrement_size, item_removed, iterator_removal, loop_bound_other, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -8057,7 +8017,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>BorneoElephant.java</t>
+          <t>Possum.java</t>
         </is>
       </c>
     </row>
@@ -8069,23 +8029,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>loop_bound_data_length, one_loop_solution</t>
+          <t>loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SeaTurtle.java | Starfish.java</t>
+          <t>Scyphozoa.java</t>
         </is>
       </c>
     </row>
@@ -8097,23 +8057,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_data_length, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E146" t="b">
         <v>1</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Crustacea.java | SiberianTiger.java</t>
+          <t>ArcticWolf.java | Bivalvia.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | FlyingSquirrel.java | Frigatebird.java | GreyReefShark.java | HoneyBee.java | HornedFrog.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | Lizard.java | Manatee.java | MarineToad.java | MountainGorilla.java | Ostrich.java | RedKneeTarantula.java | SpectacledBear.java | StellersSeaCow.java | Tapir.java | TreeFrog.java | Wasp.java | Woodpecker.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -8125,23 +8085,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Incorrect: `remove` does not visibly decrement `size`, so deleting an element can leave the logical count too large. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. The code nulls out array slots, but nulling a slot is not the same as reducing `size`; without a decrement, the field becomes inaccurate.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>loop_bound_other, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SeaDragon.java</t>
+          <t>AfricanPenguin.java | Bandicoot.java | Bullfrog.java | Dormouse.java | Kakapo.java | Lionfish.java | Mammalia.java | Mole.java | Rabbit.java | SourcingOurContent.java | SumatranTiger.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -8153,23 +8113,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>loop_bound_other, one_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>IndianPalmSquirrel.java</t>
+          <t>Chicken.java | PatasMonkey.java | SeaUrchin.java</t>
         </is>
       </c>
     </row>
@@ -8181,23 +8141,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Opossum.java</t>
+          <t>LeopardTortoise.java | Seahorse.java | Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -8209,23 +8169,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>loop_bound_other, one_loop_solution</t>
+          <t>loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D150" t="n">
         <v>2</v>
       </c>
       <c r="E150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tiger.java | Yak.java</t>
+          <t>Hare.java | SeaOtter.java</t>
         </is>
       </c>
     </row>
@@ -8237,23 +8197,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, iterator_removal, loop_bound_other, one_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Possum.java</t>
+          <t>MaskedPalmCivet.java | SriLankanElephant.java</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8225,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>loop_bound_data_length, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -8281,7 +8241,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Scyphozoa.java</t>
+          <t>BumbleBee.java</t>
         </is>
       </c>
     </row>
@@ -8298,18 +8258,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
+          <t>loop_bound_size, one_loop_solution</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ArcticWolf.java | Bivalvia.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | FlyingSquirrel.java | Frigatebird.java | GreyReefShark.java | HoneyBee.java | HornedFrog.java | KeelBilledToucan.java | Kiwi.java | Lizard.java | Manatee.java | MarineToad.java | MountainGorilla.java | Ostrich.java | RedKneeTarantula.java | StellersSeaCow.java | Tapir.java | TreeFrog.java | Woodpecker.java | Zorse.java</t>
+          <t>Dolphin.java</t>
         </is>
       </c>
     </row>
@@ -8326,18 +8286,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Bandicoot.java | Kakapo.java | Lionfish.java | Mole.java | Rabbit.java | SourcingOurContent.java | SumatranTiger.java | YellowEyedPenguin.java</t>
+          <t>IndochineseTiger.java</t>
         </is>
       </c>
     </row>
@@ -8354,18 +8314,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Chicken.java | PatasMonkey.java | SeaUrchin.java</t>
+          <t>Moorhen.java</t>
         </is>
       </c>
     </row>
@@ -8382,18 +8342,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LeopardTortoise.java | Seahorse.java | Urochordata.java</t>
+          <t>SabreToothedTiger.java</t>
         </is>
       </c>
     </row>
@@ -8405,23 +8365,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_other, two_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bullfrog.java | Dormouse.java</t>
+          <t>Anthozoa.java | Armadillo.java | AsiaticBlackBear.java | Cichlid.java | Discus.java | FrilledLizard.java | Grasshopper.java | Llama.java | OurPolicies.java | Porcupine.java | Salamander.java | SiameseFightingFish.java | Skunk.java | Sparrow.java | SunBear.java</t>
         </is>
       </c>
     </row>
@@ -8433,23 +8393,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MaskedPalmCivet.java | SriLankanElephant.java</t>
+          <t>Amphibia.java | Centipede.java | Cuttlefish.java | Gorilla.java | Panther.java | SumatranElephant.java</t>
         </is>
       </c>
     </row>
@@ -8461,23 +8421,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>loop_bound_other, loop_bound_size, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>BumbleBee.java</t>
+          <t>AsianGiantHornet.java | LeopardCat.java</t>
         </is>
       </c>
     </row>
@@ -8489,23 +8449,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>loop_bound_size, one_loop_solution</t>
+          <t>loop_bound_other, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dolphin.java</t>
+          <t>Hamster.java | NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8477,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8526,14 +8486,14 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hare.java</t>
+          <t>Impala.java | Parrot.java</t>
         </is>
       </c>
     </row>
@@ -8545,23 +8505,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>loop_bound_data_length, loop_bound_other, two_loop_solution, uses_contains</t>
+          <t>loop_bound_size, one_loop_solution</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>IndochineseTiger.java</t>
+          <t>Rhinoceros.java | WaterBuffalo.java</t>
         </is>
       </c>
     </row>
@@ -8573,23 +8533,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, loop_bound_size, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kingfisher.java</t>
+          <t>Robin.java | Tetra.java</t>
         </is>
       </c>
     </row>
@@ -8601,12 +8561,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>array_reconstruction, decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -8617,7 +8577,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mammalia.java</t>
+          <t>Baboon.java</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8589,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>loop_bound_other, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -8645,7 +8605,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Moorhen.java</t>
+          <t>Caterpillar.java</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8617,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_other, two_loop_solution</t>
+          <t>loop_bound_other, two_loop_solution</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -8673,7 +8633,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SabreToothedTiger.java</t>
+          <t>CrabEatingMacaque.java</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8645,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>loop_bound_other, two_loop_solution</t>
+          <t>loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -8701,7 +8661,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SeaOtter.java</t>
+          <t>CrestedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8673,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -8729,7 +8689,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SpectacledBear.java</t>
+          <t>HighlandCattle.java</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8701,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_other, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -8757,7 +8717,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wasp.java</t>
+          <t>IndianRhinoceros.java</t>
         </is>
       </c>
     </row>
@@ -8774,18 +8734,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution</t>
+          <t>loop_bound_data_length, loop_bound_size, two_loop_solution</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anthozoa.java | Armadillo.java | AsiaticBlackBear.java | Cichlid.java | Discus.java | FrilledLizard.java | Grasshopper.java | Llama.java | OurPolicies.java | Porcupine.java | Salamander.java | SiameseFightingFish.java | Skunk.java | Sparrow.java</t>
+          <t>Orangutan.java</t>
         </is>
       </c>
     </row>
@@ -8802,18 +8762,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Amphibia.java | Centipede.java | Cuttlefish.java | Gorilla.java | SumatranElephant.java</t>
+          <t>Platypus.java</t>
         </is>
       </c>
     </row>
@@ -8830,18 +8790,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>loop_bound_other, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CrabEatingMacaque.java | Impala.java | Orangutan.java</t>
+          <t>Uakari.java</t>
         </is>
       </c>
     </row>
@@ -8853,23 +8813,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, two_loop_solution</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>2</v>
       </c>
       <c r="E173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AsianGiantHornet.java | LeopardCat.java</t>
+          <t>Goose.java | Prawn.java</t>
         </is>
       </c>
     </row>
@@ -8881,23 +8841,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>loop_bound_other, loop_bound_size, two_loop_solution</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hamster.java | NurseShark.java</t>
+          <t>Okapi.java</t>
         </is>
       </c>
     </row>
@@ -8909,180 +8869,180 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution, uses_contains</t>
+          <t>decrement_size, item_removed, loop_bound_data_length, two_loop_solution</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>IndianRhinoceros.java | Panther.java</t>
+          <t>AfricanWildDog.java</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>The method does not reveal a clear size-maintenance strategy from static inspection.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_other, two_loop_solution</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Platypus.java | SunBear.java</t>
+          <t>CrestedPenguin.java</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` adjusts `size` directly; that is only correct if it decrements once per element truly removed.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>loop_bound_size, one_loop_solution</t>
+          <t>calls_contains, decrements_size, does_not_call_remove, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rhinoceros.java | WaterBuffalo.java</t>
+          <t>RedKneeTarantula.java</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>array_reconstruction, decrement_size, item_removed, loop_bound_size, one_loop_solution, uses_contains</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Baboon.java</t>
+          <t>Dugong.java | GreenBeeEater.java | Monkey.java | Quokka.java | SeaDragon.java | SlowWorm.java | Starfish.java</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>loop_bound_other, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Caterpillar.java</t>
+          <t>BlackRhinoceros.java | SeaTurtle.java</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CrestedPenguin.java</t>
+          <t>Bobcat.java | Catfish.java</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_size, one_loop_solution</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -9093,24 +9053,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HighlandCattle.java</t>
+          <t>Crustacea.java</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>loop_bound_size, two_loop_solution</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -9121,175 +9081,175 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Parrot.java</t>
+          <t>SiberianTiger.java</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D183" t="n">
         <v>1</v>
       </c>
       <c r="E183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Robin.java</t>
+          <t>BorneoElephant.java</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>item_removed, loop_bound_data_length, loop_bound_other, two_loop_solution</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tetra.java</t>
+          <t>AfricanPenguin.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | Bullfrog.java | BumbleBee.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | FrilledLizard.java | Goose.java | Grasshopper.java | Hare.java | HoneyBee.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | Manatee.java | MaskedPalmCivet.java | Mole.java | MountainGorilla.java | Okapi.java | Opossum.java | Orangutan.java | OurPolicies.java | Parrot.java | Platypus.java | Porcupine.java | Possum.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SpectacledBear.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | Tetra.java | Tiger.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It searches/shifts within the prefix bounded by `size`, which matches the logical occupied region. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Uakari.java</t>
+          <t>Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | Cichlid.java | CrabEatingMacaque.java | Gorilla.java | GreyReefShark.java | Hamster.java | Llama.java | Panther.java | PatasMonkey.java | Rabbit.java | Rhinoceros.java | SeaUrchin.java | Skunk.java | Sparrow.java | SunBear.java | Wasp.java</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, two_loop_solution</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Goose.java | Prawn.java</t>
+          <t>AfricanWildDog.java | Amphibia.java | Caterpillar.java | Centipede.java | Chicken.java | Cuttlefish.java | HornedFrog.java | KeelBilledToucan.java | Kingfisher.java | LeopardTortoise.java | Lionfish.java | Lizard.java | SeaOtter.java | SiameseFightingFish.java | SourcingOurContent.java | TreeFrog.java</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It also nulls or shifts slots to keep the physical array layout consistent after the logical count drops.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, loop_bound_size, two_loop_solution, uses_contains</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Okapi.java</t>
+          <t>Bivalvia.java | LeopardCat.java | Mammalia.java | MarineToad.java | Prawn.java</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>removeAll</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>`remove` decrements `size` when a deletion succeeds, which is the core requirement for keeping the logical count accurate. It uses `.length` as a search or shift boundary, so the method treats capacity as though it were occupancy. That is a separate boundary bug even if `size` were updated correctly. It reduces `size`, but because the trailing slot is not obviously cleared, stale references may remain beyond the new logical end. That does not usually make `size` inaccurate, but it can interact badly with methods that scan past `size`.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>decrement_size, item_removed, loop_bound_data_length, two_loop_solution</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java</t>
+          <t>Bandicoot.java | Newt.java</t>
         </is>
       </c>
     </row>
@@ -9301,23 +9261,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>The method does not reveal a clear size-maintenance strategy from static inspection.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CrestedPenguin.java</t>
+          <t>Frigatebird.java | Moorhen.java</t>
         </is>
       </c>
     </row>
@@ -9329,23 +9289,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>`removeAll` adjusts `size` directly; that is only correct if it decrements once per element truly removed.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>calls_contains, decrements_size, does_not_call_remove, loop_over_self_collection</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D190" t="n">
         <v>1</v>
       </c>
       <c r="E190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>RedKneeTarantula.java</t>
+          <t>HighlandCattle.java</t>
         </is>
       </c>
     </row>
@@ -9357,23 +9317,23 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dugong.java | GreenBeeEater.java | Monkey.java | Quokka.java | SeaDragon.java | SlowWorm.java | Starfish.java</t>
+          <t>Ostrich.java</t>
         </is>
       </c>
     </row>
@@ -9385,23 +9345,23 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D192" t="n">
         <v>2</v>
       </c>
       <c r="E192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>BlackRhinoceros.java | SeaTurtle.java</t>
+          <t>NurseShark.java | Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9373,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
+          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -9429,7 +9389,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bobcat.java | Catfish.java</t>
+          <t>SriLankanElephant.java | Tapir.java</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9401,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
+          <t>`removeAll` relies on iterator-based deletion, so the `size` behavior depends on whether iterator `remove()` updates the count exactly once.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9450,14 +9410,14 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Crustacea.java</t>
+          <t>IndochineseTiger.java | Kakapo.java | Kiwi.java | Seahorse.java</t>
         </is>
       </c>
     </row>
@@ -9469,12 +9429,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems.</t>
+          <t>`removeAll` relies on iterator-based deletion, so the `size` behavior depends on whether iterator `remove()` updates the count exactly once.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -9485,192 +9445,192 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SiberianTiger.java</t>
+          <t>FlyingSquirrel.java</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` is flawed in this submission, `removeAll` inherits those size-accounting problems. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection, loop_over_self_collection</t>
+          <t>calls_contains, does_not_call_remove, loop_other, size_no_update</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="b">
         <v>1</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BorneoElephant.java</t>
+          <t>Gorilla.java | Mammalia.java</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection</t>
+          <t>does_not_call_contains, does_not_call_remove, size_no_update</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="E197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Armadillo.java | AsianGiantHornet.java | Baboon.java | Bullfrog.java | BumbleBee.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | FrilledLizard.java | Goose.java | Grasshopper.java | Hare.java | HoneyBee.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | Manatee.java | MaskedPalmCivet.java | Mole.java | MountainGorilla.java | Okapi.java | Opossum.java | Orangutan.java | OurPolicies.java | Parrot.java | Platypus.java | Porcupine.java | Possum.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SpectacledBear.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | Tetra.java | Tiger.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
+          <t>Kiwi.java | Robin.java</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
+          <t>does_not_call_contains, does_not_call_remove, loop_over_input_collection, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | Cichlid.java | CrabEatingMacaque.java | Gorilla.java | GreyReefShark.java | Hamster.java | Llama.java | Panther.java | PatasMonkey.java | Rabbit.java | Rhinoceros.java | SeaUrchin.java | Skunk.java | Sparrow.java | SunBear.java | Wasp.java</t>
+          <t>Dolphin.java</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java | Amphibia.java | Caterpillar.java | Centipede.java | Chicken.java | Cuttlefish.java | HornedFrog.java | KeelBilledToucan.java | Kingfisher.java | LeopardTortoise.java | Lionfish.java | Lizard.java | SeaOtter.java | SiameseFightingFish.java | SourcingOurContent.java | TreeFrog.java</t>
+          <t>FlyingSquirrel.java</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bivalvia.java | LeopardCat.java | Mammalia.java | MarineToad.java | Prawn.java</t>
+          <t>Kakapo.java</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
+          <t>does_not_call_contains, does_not_call_remove, loop_other, loop_over_input_collection, size_no_update</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Frigatebird.java | Moorhen.java</t>
+          <t>Opossum.java</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection, loop_over_self_collection</t>
+          <t>does_not_call_contains, does_not_call_remove, loop_over_input_collection, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -9681,131 +9641,131 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bandicoot.java</t>
+          <t>Starfish.java</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>`retainAll` decrements `size` directly while filtering, which can be correct if done once per removed element.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
+          <t>calls_contains, decrements_size, does_not_call_remove, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>HighlandCattle.java</t>
+          <t>Hare.java | RedKneeTarantula.java</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach.</t>
+          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_input_collection</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ostrich.java</t>
+          <t>Centipede.java | Cuttlefish.java | Platypus.java</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
+          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>NurseShark.java | Urochordata.java</t>
+          <t>HighlandCattle.java</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>`removeAll` mostly delegates actual deletion to `remove`, so it normally does not need its own `size` arithmetic. Because `remove` updates `size` correctly, this delegation is the right approach. It also mixes in `.length`/capacity logic, which can make bulk removal depend on null layout instead of the `size` prefix.</t>
+          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206" t="b">
         <v>0</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SriLankanElephant.java | Tapir.java</t>
+          <t>KeelBilledToucan.java</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>`removeAll` relies on iterator-based deletion, so the `size` behavior depends on whether iterator `remove()` updates the count exactly once.</t>
+          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9814,26 +9774,26 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>IndochineseTiger.java | Kakapo.java | Kiwi.java | Seahorse.java</t>
+          <t>LeopardCat.java</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>removeAll</t>
+          <t>retainAll</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>`removeAll` relies on iterator-based deletion, so the `size` behavior depends on whether iterator `remove()` updates the count exactly once.</t>
+          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has. Since `remove` is not reliable here, `retainAll` is also suspect.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9845,11 +9805,11 @@
         <v>1</v>
       </c>
       <c r="E208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FlyingSquirrel.java</t>
+          <t>Quokka.java</t>
         </is>
       </c>
     </row>
@@ -9861,23 +9821,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_other, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E209" t="b">
         <v>1</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gorilla.java | Mammalia.java</t>
+          <t>IndianPalmSquirrel.java | SeaUrchin.java | Tiger.java</t>
         </is>
       </c>
     </row>
@@ -9889,12 +9849,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>does_not_call_contains, does_not_call_remove, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -9905,7 +9865,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kiwi.java | Robin.java</t>
+          <t>Dormouse.java | SeaDragon.java</t>
         </is>
       </c>
     </row>
@@ -9917,12 +9877,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>does_not_call_contains, does_not_call_remove, loop_over_input_collection, loop_over_self_collection, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -9933,7 +9893,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dolphin.java</t>
+          <t>MountainGorilla.java</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9905,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
+          <t>does_not_call_contains, does_not_call_remove, loop_over_self_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -9961,7 +9921,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FlyingSquirrel.java</t>
+          <t>Newt.java</t>
         </is>
       </c>
     </row>
@@ -9973,12 +9933,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -9989,7 +9949,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kakapo.java</t>
+          <t>Scyphozoa.java</t>
         </is>
       </c>
     </row>
@@ -10001,23 +9961,23 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>does_not_call_contains, does_not_call_remove, loop_other, loop_over_input_collection, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_other, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D214" t="n">
         <v>1</v>
       </c>
       <c r="E214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Opossum.java</t>
+          <t>Sparrow.java</t>
         </is>
       </c>
     </row>
@@ -10029,23 +9989,23 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>The method does not expose a clear `size` strategy and seems to depend on helper behavior. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>does_not_call_contains, does_not_call_remove, loop_over_input_collection, loop_over_self_collection, size_no_update</t>
+          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Starfish.java</t>
+          <t>Dhole.java | Manatee.java | Tetra.java</t>
         </is>
       </c>
     </row>
@@ -10057,23 +10017,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>`retainAll` decrements `size` directly while filtering, which can be correct if done once per removed element.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>calls_contains, decrements_size, does_not_call_remove, loop_over_self_collection</t>
+          <t>calls_contains, does_not_call_remove, loop_other, size_no_update</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hare.java | RedKneeTarantula.java</t>
+          <t>Crustacea.java</t>
         </is>
       </c>
     </row>
@@ -10085,23 +10045,23 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
+          <t>calls_contains, does_not_call_remove, loop_other, loop_over_input_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Centipede.java | Cuttlefish.java | Platypus.java</t>
+          <t>HornedFrog.java</t>
         </is>
       </c>
     </row>
@@ -10113,12 +10073,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
+          <t>does_not_call_contains, does_not_call_remove, loop_other, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -10129,7 +10089,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>HighlandCattle.java</t>
+          <t>NurseShark.java</t>
         </is>
       </c>
     </row>
@@ -10141,12 +10101,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_input_collection</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -10157,7 +10117,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>KeelBilledToucan.java</t>
+          <t>Possum.java</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10129,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has.</t>
+          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
+          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -10185,7 +10145,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>LeopardCat.java</t>
+          <t>SabreToothedTiger.java</t>
         </is>
       </c>
     </row>
@@ -10197,12 +10157,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>`retainAll` delegates deletion to `remove`, so it inherits whatever `size` behavior `remove` has. Since `remove` is not reliable here, `retainAll` is also suspect.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. Its correctness therefore depends on the iterator implementation.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -10213,7 +10173,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Quokka.java</t>
+          <t>AfricanPenguin.java</t>
         </is>
       </c>
     </row>
@@ -10225,23 +10185,23 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E222" t="b">
         <v>1</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>IndianPalmSquirrel.java | SeaUrchin.java | Tiger.java</t>
+          <t>AfricanWildDog.java | Amphibia.java | Armadillo.java | Baboon.java | Bandicoot.java | Bivalvia.java | BumbleBee.java | Caterpillar.java | Cichlid.java | Crane.java | CrossRiverGorilla.java | Discus.java | Frigatebird.java | GreenBeeEater.java | IndianRhinoceros.java | LeopardTortoise.java | Lizard.java | Llama.java | Mole.java | Monkey.java | Moorhen.java | Rabbit.java | SeaTurtle.java | Seahorse.java | SiameseFightingFish.java | SpectacledBear.java | SunBear.java | Tapir.java | TreeFrog.java | Uakari.java | Woodpecker.java</t>
         </is>
       </c>
     </row>
@@ -10253,23 +10213,23 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
+          <t>calls_contains, calls_remove, calls_remove_only, iterator_removal, loop_other</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E223" t="b">
         <v>0</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dormouse.java | SeaDragon.java</t>
+          <t>Anthozoa.java | Crab.java | CrestedPenguin.java | Deer.java | Grasshopper.java | GreyReefShark.java | IndochineseTiger.java | MaskedPalmCivet.java | Okapi.java | Panther.java | PatasMonkey.java | Porcupine.java | Prawn.java | Rhinoceros.java | Salamander.java | SeaOtter.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | StellersSeaCow.java | SumatranTiger.java | WaterBuffalo.java | Zorse.java</t>
         </is>
       </c>
     </row>
@@ -10281,23 +10241,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_change_nonstandard</t>
+          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E224" t="b">
         <v>0</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>MountainGorilla.java</t>
+          <t>AsianGiantHornet.java | Bobcat.java | Catfish.java | Cow.java | Kingfisher.java | Ostrich.java</t>
         </is>
       </c>
     </row>
@@ -10309,23 +10269,23 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E225" t="b">
         <v>0</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Scyphozoa.java</t>
+          <t>BorneoElephant.java | Chicken.java | FrilledLizard.java | Impala.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
@@ -10337,23 +10297,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_other, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E226" t="b">
         <v>0</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sparrow.java</t>
+          <t>AsiaticBlackBear.java | BlackRhinoceros.java | CrabEatingMacaque.java</t>
         </is>
       </c>
     </row>
@@ -10365,23 +10325,23 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other</t>
         </is>
       </c>
       <c r="D227" t="n">
         <v>2</v>
       </c>
       <c r="E227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Dhole.java | Manatee.java</t>
+          <t>ArcticWolf.java | MarineToad.java</t>
         </is>
       </c>
     </row>
@@ -10393,23 +10353,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_other, size_no_update</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="b">
         <v>0</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Crustacea.java</t>
+          <t>Hamster.java | Wasp.java</t>
         </is>
       </c>
     </row>
@@ -10421,23 +10381,23 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_other, loop_over_input_collection, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" t="b">
         <v>0</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HornedFrog.java</t>
+          <t>HoneyBee.java | Parrot.java</t>
         </is>
       </c>
     </row>
@@ -10449,23 +10409,23 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>does_not_call_contains, does_not_call_remove, loop_other, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other, loop_over_input_collection</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="b">
         <v>0</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>NurseShark.java</t>
+          <t>Lionfish.java | OurPolicies.java</t>
         </is>
       </c>
     </row>
@@ -10477,12 +10437,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_no_update</t>
+          <t>calls_contains, calls_remove, iterator_removal, loop_other, size_change_nonstandard</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -10493,7 +10453,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Possum.java</t>
+          <t>SumatranElephant.java</t>
         </is>
       </c>
     </row>
@@ -10505,23 +10465,23 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_self_collection, size_change_nonstandard</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
         </is>
       </c>
       <c r="D232" t="n">
         <v>1</v>
       </c>
       <c r="E232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SabreToothedTiger.java</t>
+          <t>SiberianTiger.java</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10493,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>`retainAll` reasons over `size`, but it is not obvious that it updates the field correctly when elements are discarded. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>calls_contains, does_not_call_remove, loop_over_input_collection, size_no_update</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -10549,7 +10509,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tetra.java</t>
+          <t>SriLankanElephant.java</t>
         </is>
       </c>
     </row>
@@ -10561,23 +10521,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. Its correctness therefore depends on the iterator implementation.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
+          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other</t>
         </is>
       </c>
       <c r="D234" t="n">
         <v>1</v>
       </c>
       <c r="E234" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java</t>
+          <t>Urochordata.java</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10549,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is problematic here because iterator `remove()` appears not to update `size` correctly, so retained/deleted counts can become inaccurate.</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10598,14 +10558,14 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E235" t="b">
         <v>1</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java | Amphibia.java | Armadillo.java | Baboon.java | Bandicoot.java | Bivalvia.java | BumbleBee.java | Caterpillar.java | Cichlid.java | Crane.java | CrossRiverGorilla.java | Discus.java | Frigatebird.java | GreenBeeEater.java | IndianRhinoceros.java | LeopardTortoise.java | Lizard.java | Llama.java | Mole.java | Monkey.java | Moorhen.java | Rabbit.java | SeaTurtle.java | Seahorse.java | SiameseFightingFish.java | SpectacledBear.java | SunBear.java | Tapir.java | TreeFrog.java | Uakari.java | Woodpecker.java</t>
+          <t>Bullfrog.java | Orangutan.java | Yak.java</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10577,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is problematic here because iterator `remove()` appears not to update `size` correctly, so retained/deleted counts can become inaccurate.</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10626,171 +10586,163 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E236" t="b">
         <v>0</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Anthozoa.java | Crab.java | CrestedPenguin.java | Deer.java | Grasshopper.java | GreyReefShark.java | IndochineseTiger.java | MaskedPalmCivet.java | Okapi.java | Panther.java | PatasMonkey.java | Porcupine.java | Prawn.java | Rhinoceros.java | Salamander.java | SeaOtter.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | StellersSeaCow.java | SumatranTiger.java | WaterBuffalo.java | Zorse.java</t>
+          <t>Dugong.java | Goose.java</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>size</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_over_self_collection</t>
-        </is>
-      </c>
+          <t>`size()` recomputes the count by scanning the array for non-null entries instead of trusting the `size` field. That can hide bugs in `add`/`remove`, but it means the field itself is not being maintained as the authoritative logical count.</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AsianGiantHornet.java | Bobcat.java | Catfish.java | Cow.java | Kingfisher.java | Ostrich.java</t>
+          <t>BorneoElephant.java | Crustacea.java</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>size</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_input_collection</t>
-        </is>
-      </c>
+          <t>`size()` recomputes the count by scanning the array for non-null entries instead of trusting the `size` field. That can hide bugs in `add`/`remove`, but it means the field itself is not being maintained as the authoritative logical count. In this file the returned value is also post-incremented, so the method itself reports an off-by-one result.</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>BorneoElephant.java | Chicken.java | FrilledLizard.java | Impala.java | YellowEyedPenguin.java</t>
+          <t>SiberianTiger.java</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>size</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`size()` returns the `size` field directly, which is the correct interface: the field is treated as the authoritative logical element count.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
+          <t>returns_size</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="E239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AsiaticBlackBear.java | BlackRhinoceros.java | CrabEatingMacaque.java</t>
+          <t>AfricanPenguin.java | AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | CrabEatingMacaque.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | Newt.java | NurseShark.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | OurPolicies.java | Panther.java | Parrot.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | Seahorse.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | Urochordata.java | Wasp.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>The array-conversion boundary is not obvious from static inspection.</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other</t>
+          <t>no_loop</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>ArcticWolf.java | MarineToad.java</t>
+          <t>Prawn.java</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`toArray` uses `.length` or whole-array traversal, so it risks exporting unused capacity slots or relying on null layout instead of the `size` prefix.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other, loop_over_self_collection</t>
+          <t>loop_bound_data_length, returns_new_array, uses_loop_copy</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Hamster.java | Wasp.java</t>
+          <t>Crustacea.java | Kakapo.java | Kingfisher.java | PatasMonkey.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`toArray` uses `.length` or whole-array traversal, so it risks exporting unused capacity slots or relying on null layout instead of the `size` prefix.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_input_collection, loop_over_self_collection</t>
+          <t>loop_bound_other, returns_new_array, uses_loop_copy</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -10801,464 +10753,472 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>HoneyBee.java | Parrot.java</t>
+          <t>Goose.java | IndianPalmSquirrel.java</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other, loop_over_input_collection</t>
+          <t>loop_bound_size, returns_new_array, uses_loop_copy</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="E243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Lionfish.java | OurPolicies.java</t>
+          <t>AfricanPenguin.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | Crane.java | CrestedPenguin.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dormouse.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | Impala.java | IndochineseTiger.java | KeelBilledToucan.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | NurseShark.java | Okapi.java | Opossum.java | Orangutan.java | Ostrich.java | Panther.java | Parrot.java | Platypus.java | Porcupine.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SeaDragon.java | SeaOtter.java | SeaTurtle.java | SeaUrchin.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | Tetra.java | Tiger.java | TreeFrog.java | Uakari.java | Wasp.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once.</t>
+          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, iterator_removal, loop_other, size_change_nonstandard</t>
+          <t>loop_bound_other, returns_new_array, uses_loop_copy</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E244" t="b">
         <v>0</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SumatranElephant.java</t>
+          <t>Armadillo.java | AsianGiantHornet.java | BorneoElephant.java | CrabEatingMacaque.java | IndianRhinoceros.java | Newt.java | OurPolicies.java | Possum.java | Urochordata.java</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_over_self_collection</t>
+          <t>loop_bound_data_length, returns_new_array, uses_loop_copy</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SiberianTiger.java</t>
+          <t>FrilledLizard.java | Seahorse.java | Sparrow.java | SpectacledBear.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toArray</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, loop_other</t>
+          <t>no_loop, returns_new_array</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" t="b">
         <v>0</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SriLankanElephant.java</t>
+          <t>AfricanWildDog.java | Baboon.java</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is correct because iterator removal is already responsible for updating `size` exactly once. It also uses capacity-oriented boundaries in places, which is weaker than consistently trusting `size` as the logical prefix length.</t>
+          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>calls_remove, calls_remove_only, does_not_call_contains, iterator_removal, loop_other</t>
+          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Urochordata.java</t>
+          <t>AsianGiantHornet.java | AsiaticBlackBear.java | Bivalvia.java | BlackRhinoceros.java | Cuttlefish.java | Dhole.java | FlyingSquirrel.java | Hare.java | KeelBilledToucan.java | Mammalia.java | Manatee.java | Okapi.java | OurPolicies.java | SeaDragon.java | Seahorse.java | WaterBuffalo.java | Yak.java | Zorse.java</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is problematic here because iterator `remove()` appears not to update `size` correctly, so retained/deleted counts can become inaccurate.</t>
+          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, loop_other</t>
+          <t>ignores_size_in_sort_scope, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bullfrog.java | Orangutan.java | Yak.java</t>
+          <t>Grasshopper.java | Salamander.java | SeaUrchin.java | Tapir.java</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>retainAll</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>`retainAll` removes unwanted elements through the iterator path rather than doing separate `size` arithmetic in the loop. That is problematic here because iterator `remove()` appears not to update `size` correctly, so retained/deleted counts can become inaccurate.</t>
+          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>calls_contains, calls_remove, calls_remove_only, iterator_removal, loop_other</t>
+          <t>loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" t="b">
         <v>0</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Dugong.java | Goose.java</t>
+          <t>Dolphin.java</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>`size()` recomputes the count by scanning the array for non-null entries instead of trusting the `size` field. That can hide bugs in `add`/`remove`, but it means the field itself is not being maintained as the authoritative logical count.</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
+          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
+        </is>
+      </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>BorneoElephant.java | Crustacea.java</t>
+          <t>Opossum.java</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>`size()` recomputes the count by scanning the array for non-null entries instead of trusting the `size` field. That can hide bugs in `add`/`remove`, but it means the field itself is not being maintained as the authoritative logical count. In this file the returned value is also post-incremented, so the method itself reports an off-by-one result.</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
+        </is>
+      </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E251" t="b">
         <v>1</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SiberianTiger.java</t>
+          <t>AfricanPenguin.java | Bobcat.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Crab.java | CrestedPenguin.java | CrossRiverGorilla.java | Deer.java | Frigatebird.java | FrilledLizard.java | Gorilla.java | IndianPalmSquirrel.java | IndochineseTiger.java | Kingfisher.java | LeopardCat.java | Lizard.java | MaskedPalmCivet.java | Mole.java | Monkey.java | NurseShark.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | SiameseFightingFish.java | Skunk.java | SourcingOurContent.java | Starfish.java | Tetra.java | Tiger.java | Uakari.java | Woodpecker.java</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>`size()` returns the `size` field directly, which is the correct interface: the field is treated as the authoritative logical element count.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>returns_size</t>
+          <t>loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>AfricanWildDog.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | Armadillo.java | AsianGiantHornet.java | AsiaticBlackBear.java | Baboon.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | FrilledLizard.java | Goose.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | IndianPalmSquirrel.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | KeelBilledToucan.java | Kingfisher.java | Kiwi.java | LeopardCat.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | NurseShark.java | Okapi.java | Opossum.java | Ostrich.java | OurPolicies.java | PatasMonkey.java | Platypus.java | Porcupine.java | Possum.java | Prawn.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Salamander.java | Scyphozoa.java | SeaTurtle.java | Seahorse.java | Skunk.java | SourcingOurContent.java | Sparrow.java | SpectacledBear.java | SriLankanElephant.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | Tapir.java | TreeFrog.java | Urochordata.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java | Zorse.java</t>
+          <t>Amphibia.java | Anthozoa.java | Armadillo.java | BumbleBee.java | Crane.java | Discus.java | Dugong.java | Goose.java | GreyReefShark.java | Hamster.java | HighlandCattle.java | HornedFrog.java | IndianRhinoceros.java | Lionfish.java | Llama.java | Orangutan.java | Panther.java | Parrot.java | PatasMonkey.java | Porcupine.java | Quokka.java | RedKneeTarantula.java | Scyphozoa.java | SlowWorm.java | SriLankanElephant.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | TreeFrog.java | Wasp.java | YellowEyedPenguin.java</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>`size()` returns the `size` field directly, which is the correct interface: the field is treated as the authoritative logical element count.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>returns_this_size</t>
+          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E253" t="b">
         <v>0</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | CrabEatingMacaque.java | CrestedPenguin.java | Dolphin.java | Dormouse.java | HornedFrog.java | Impala.java | LeopardTortoise.java | Orangutan.java | Panther.java | Parrot.java | Robin.java | SabreToothedTiger.java | SeaDragon.java | SeaOtter.java | SeaUrchin.java | SiameseFightingFish.java | SlowWorm.java | Starfish.java | SunBear.java | Tetra.java | Tiger.java | Uakari.java | Wasp.java</t>
+          <t>ArcticWolf.java | Bandicoot.java | CrabEatingMacaque.java | Impala.java | Kakapo.java | LeopardTortoise.java | Moorhen.java | MountainGorilla.java | Newt.java | Ostrich.java | Platypus.java | Possum.java | Rabbit.java | SeaOtter.java</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>The array-conversion boundary is not obvious from static inspection.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>no_loop</t>
+          <t>loop_bound_data_length, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D254" t="n">
         <v>1</v>
       </c>
       <c r="E254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Prawn.java</t>
+          <t>Baboon.java</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>`toArray` uses `.length` or whole-array traversal, so it risks exporting unused capacity slots or relying on null layout instead of the `size` prefix.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>loop_bound_data_length, returns_new_array, uses_loop_copy</t>
+          <t>copies_elements_using_size, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Crustacea.java | Kakapo.java | Kingfisher.java | PatasMonkey.java | SiberianTiger.java</t>
+          <t>Cow.java</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>`toArray` uses `.length` or whole-array traversal, so it risks exporting unused capacity slots or relying on null layout instead of the `size` prefix.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>loop_bound_other, returns_new_array, uses_loop_copy</t>
+          <t>copies_elements_using_size, loop_bound_data_length, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" t="b">
         <v>0</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Goose.java | IndianPalmSquirrel.java</t>
+          <t>MarineToad.java</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
+          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>loop_bound_size, returns_new_array, uses_loop_copy</t>
+          <t>loop_bound_data_length, loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="E257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AfricanPenguin.java | Amphibia.java | Anthozoa.java | ArcticWolf.java | AsiaticBlackBear.java | Bandicoot.java | Bivalvia.java | BlackRhinoceros.java | Bobcat.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Cow.java | Crab.java | Crane.java | CrossRiverGorilla.java | Cuttlefish.java | Deer.java | Dhole.java | Discus.java | Dolphin.java | Dugong.java | FlyingSquirrel.java | Frigatebird.java | Gorilla.java | Grasshopper.java | GreenBeeEater.java | GreyReefShark.java | Hamster.java | Hare.java | HighlandCattle.java | HoneyBee.java | HornedFrog.java | KeelBilledToucan.java | Kiwi.java | LeopardCat.java | LeopardTortoise.java | Lionfish.java | Lizard.java | Llama.java | Mammalia.java | Manatee.java | MarineToad.java | MaskedPalmCivet.java | Mole.java | Monkey.java | Moorhen.java | MountainGorilla.java | NurseShark.java | Okapi.java | Opossum.java | Ostrich.java | Parrot.java | Platypus.java | Porcupine.java | Quokka.java | Rabbit.java | RedKneeTarantula.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | Salamander.java | Scyphozoa.java | SeaTurtle.java | SeaUrchin.java | SiameseFightingFish.java | Skunk.java | SlowWorm.java | SourcingOurContent.java | SriLankanElephant.java | Starfish.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | SunBear.java | Tapir.java | TreeFrog.java | Uakari.java | WaterBuffalo.java | Woodpecker.java | Yak.java | YellowEyedPenguin.java</t>
+          <t>SeaTurtle.java</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
+          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>loop_bound_other, returns_new_array, uses_loop_copy</t>
+          <t>ignores_size_in_sort_scope, loop_bound_data_length, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Armadillo.java | AsianGiantHornet.java | BorneoElephant.java | Bullfrog.java | BumbleBee.java | Caterpillar.java | CrabEatingMacaque.java | CrestedPenguin.java | Dormouse.java | Impala.java | IndianRhinoceros.java | IndochineseTiger.java | Orangutan.java | OurPolicies.java | Panther.java | Possum.java | SeaDragon.java | SeaOtter.java | Tetra.java | Tiger.java | Urochordata.java | Wasp.java</t>
+          <t>AfricanWildDog.java | BorneoElephant.java | Bullfrog.java | Crustacea.java | Dormouse.java | Sparrow.java | SpectacledBear.java | Urochordata.java</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
+          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>loop_bound_data_length, returns_new_array, uses_loop_copy</t>
+          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -11269,24 +11229,24 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FrilledLizard.java | Seahorse.java | Sparrow.java | SpectacledBear.java | Zorse.java</t>
+          <t>Caterpillar.java | GreenBeeEater.java | HoneyBee.java | Kiwi.java | SiberianTiger.java</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>toArray</t>
+          <t>toSortedList</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>`toArray` uses `size` to determine how many logical elements to export, which is the correct distinction between occupancy and capacity.</t>
+          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>no_loop, returns_new_array</t>
+          <t>ignores_size_in_sort_scope, loop_bound_data_length, loop_bound_other, size_not_mutated_in_toSortedList</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -11296,398 +11256,6 @@
         <v>0</v>
       </c>
       <c r="F260" t="inlineStr">
-        <is>
-          <t>AfricanWildDog.java | Baboon.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>18</v>
-      </c>
-      <c r="E261" t="b">
-        <v>1</v>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>AsianGiantHornet.java | AsiaticBlackBear.java | Bivalvia.java | BlackRhinoceros.java | Cuttlefish.java | Dhole.java | FlyingSquirrel.java | Hare.java | KeelBilledToucan.java | Mammalia.java | Manatee.java | Okapi.java | OurPolicies.java | SeaDragon.java | Seahorse.java | WaterBuffalo.java | Yak.java | Zorse.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>4</v>
-      </c>
-      <c r="E262" t="b">
-        <v>0</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Grasshopper.java | Salamander.java | SeaUrchin.java | Tapir.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" t="b">
-        <v>0</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Dolphin.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>The method's size boundary is not obvious from static inspection. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>1</v>
-      </c>
-      <c r="E264" t="b">
-        <v>0</v>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Opossum.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>28</v>
-      </c>
-      <c r="E265" t="b">
-        <v>1</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>AfricanPenguin.java | Bobcat.java | Catfish.java | Centipede.java | Chicken.java | Cichlid.java | Crab.java | CrestedPenguin.java | CrossRiverGorilla.java | Deer.java | Frigatebird.java | Gorilla.java | IndianPalmSquirrel.java | Kingfisher.java | LeopardCat.java | Lizard.java | Mole.java | Monkey.java | NurseShark.java | Rhinoceros.java | Robin.java | SabreToothedTiger.java | SiameseFightingFish.java | Skunk.java | SourcingOurContent.java | Starfish.java | Tiger.java | Woodpecker.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>25</v>
-      </c>
-      <c r="E266" t="b">
-        <v>0</v>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Amphibia.java | Anthozoa.java | Armadillo.java | Crane.java | Discus.java | Dugong.java | Goose.java | GreyReefShark.java | Hamster.java | HighlandCattle.java | HornedFrog.java | Lionfish.java | Llama.java | PatasMonkey.java | Porcupine.java | Quokka.java | RedKneeTarantula.java | Scyphozoa.java | SlowWorm.java | SriLankanElephant.java | StellersSeaCow.java | SumatranElephant.java | SumatranTiger.java | TreeFrog.java | YellowEyedPenguin.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>24</v>
-      </c>
-      <c r="E267" t="b">
-        <v>0</v>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>ArcticWolf.java | Bandicoot.java | BumbleBee.java | CrabEatingMacaque.java | FrilledLizard.java | Impala.java | IndianRhinoceros.java | IndochineseTiger.java | Kakapo.java | LeopardTortoise.java | MaskedPalmCivet.java | Moorhen.java | MountainGorilla.java | Orangutan.java | Ostrich.java | Panther.java | Parrot.java | Platypus.java | Possum.java | Rabbit.java | SeaOtter.java | Tetra.java | Uakari.java | Wasp.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>loop_bound_data_length, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" t="b">
-        <v>0</v>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Baboon.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>copies_elements_using_size, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" t="b">
-        <v>0</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Cow.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>copies_elements_using_size, loop_bound_data_length, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" t="b">
-        <v>0</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>MarineToad.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>`toSortedList` copies or visits only the first `size` elements before sorting, which is correct because only that prefix is logically populated. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>loop_bound_data_length, loop_bound_other, loop_bound_size, size_not_mutated_in_toSortedList, uses_size_to_limit_sort_scope</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" t="b">
-        <v>0</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>SeaTurtle.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, loop_bound_other, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>7</v>
-      </c>
-      <c r="E272" t="b">
-        <v>1</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Bullfrog.java | Caterpillar.java | Dormouse.java | GreenBeeEater.java | HoneyBee.java | Kiwi.java | SiberianTiger.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, loop_bound_data_length, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>6</v>
-      </c>
-      <c r="E273" t="b">
-        <v>0</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>AfricanWildDog.java | BorneoElephant.java | Crustacea.java | Sparrow.java | SpectacledBear.java | Urochordata.java</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>toSortedList</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>`toSortedList` traverses the whole backing array or uses `.length`, so it confuses capacity with the logical collection contents. It should not change `size`, and this implementation does not obviously mutate the field.</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>ignores_size_in_sort_scope, loop_bound_data_length, loop_bound_other, size_not_mutated_in_toSortedList</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>2</v>
-      </c>
-      <c r="E274" t="b">
-        <v>0</v>
-      </c>
-      <c r="F274" t="inlineStr">
         <is>
           <t>Prawn.java | SunBear.java</t>
         </is>
